--- a/automation/reports/Excel/Security_Vulnerability_Test_Report.xlsx
+++ b/automation/reports/Excel/Security_Vulnerability_Test_Report.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="639">
   <si>
-    <t>Smart Ulcer Predictor — Security &amp; Vulnerability Test Report — Executed Test Cases — 2026-08-25 16:43:14</t>
+    <t>Smart Ulcer Predictor — Security &amp; Vulnerability Test Report — Executed Test Cases — 2026-08-25 17:00:08</t>
   </si>
   <si>
     <t>Test ID</t>
